--- a/src/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_lattice.xlsx
+++ b/src/nodes/LPC/compressor_stage_3_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-24.399701373012373</v>
+        <v>-24.459060444860274</v>
       </c>
       <c r="B1">
-        <v>24.267017410588384</v>
+        <v>24.207187429617946</v>
       </c>
       <c r="C1">
         <v>338.16769933532214</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-21.500645105215604</v>
+        <v>-21.787322175970527</v>
       </c>
       <c r="B2">
-        <v>23.987060496608777</v>
+        <v>23.776935434152676</v>
       </c>
       <c r="C2">
         <v>338.16769933532214</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-19.35383767967302</v>
+        <v>-19.724838707075822</v>
       </c>
       <c r="B3">
-        <v>23.190505427322027</v>
+        <v>22.9260852521317</v>
       </c>
       <c r="C3">
         <v>338.16769933532214</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-17.346986581060353</v>
+        <v>-17.782357272709675</v>
       </c>
       <c r="B4">
-        <v>22.297836976060644</v>
+        <v>21.992391835874219</v>
       </c>
       <c r="C4">
         <v>338.16769933532214</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-15.445040244130198</v>
+        <v>-15.931663593671271</v>
       </c>
       <c r="B5">
-        <v>21.333126398146437</v>
+        <v>20.995332872986371</v>
       </c>
       <c r="C5">
         <v>338.16769933532214</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-13.633167005967602</v>
+        <v>-14.16071245164847</v>
       </c>
       <c r="B6">
-        <v>20.306559165821589</v>
+        <v>19.943223762836013</v>
       </c>
       <c r="C6">
         <v>338.16769933532214</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-11.90259656397893</v>
+        <v>-12.46232319713803</v>
       </c>
       <c r="B7">
-        <v>19.224158182528242</v>
+        <v>18.841021656617333</v>
       </c>
       <c r="C7">
         <v>338.16769933532214</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-10.247869503062109</v>
+        <v>-10.831970293731661</v>
       </c>
       <c r="B8">
-        <v>18.089672638178527</v>
+        <v>17.691850751967408</v>
       </c>
       <c r="C8">
         <v>338.16769933532214</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-8.661019562854456</v>
+        <v>-9.2631486280060944</v>
       </c>
       <c r="B9">
-        <v>16.908573269551141</v>
+        <v>16.500201844706279</v>
       </c>
       <c r="C9">
         <v>338.16769933532214</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-7.1335519739053836</v>
+        <v>-7.748941175304572</v>
       </c>
       <c r="B10">
-        <v>15.686693760902468</v>
+        <v>15.270850092989493</v>
       </c>
       <c r="C10">
         <v>338.16769933532214</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-5.6573647756731793</v>
+        <v>-6.2827628430513132</v>
       </c>
       <c r="B11">
-        <v>14.429598039533037</v>
+        <v>14.008341506131536</v>
       </c>
       <c r="C11">
         <v>338.16769933532214</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-4.2279136451942181</v>
+        <v>-4.8608783795932515</v>
       </c>
       <c r="B12">
-        <v>13.140406866457377</v>
+        <v>12.715254709810226</v>
       </c>
       <c r="C12">
         <v>338.16769933532214</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-2.854492000908313</v>
+        <v>-3.4906199648872374</v>
       </c>
       <c r="B13">
-        <v>11.812738094501796</v>
+        <v>11.386527943997791</v>
       </c>
       <c r="C13">
         <v>338.16769933532214</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.5425191584852427</v>
+        <v>-2.176233477996643</v>
       </c>
       <c r="B14">
-        <v>10.442870071573573</v>
+        <v>10.019230072108352</v>
       </c>
       <c r="C14">
         <v>338.16769933532214</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.2680802811112345</v>
+        <v>-0.89855216280105255</v>
       </c>
       <c r="B15">
-        <v>9.0472260340919561</v>
+        <v>8.62659283702922</v>
       </c>
       <c r="C15">
         <v>338.16769933532214</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>0.99075567306324908</v>
+        <v>0.36000011125670317</v>
       </c>
       <c r="B16">
-        <v>7.6408668703256462</v>
+        <v>7.2207498955474678</v>
       </c>
       <c r="C16">
         <v>338.16769933532214</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2.218650413547286</v>
+        <v>1.5872243372970565</v>
       </c>
       <c r="B17">
-        <v>6.213259187428946</v>
+        <v>5.7932796805759406</v>
       </c>
       <c r="C17">
         <v>338.16769933532214</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>3.3956877685344384</v>
+        <v>2.7672578893385991</v>
       </c>
       <c r="B18">
-        <v>4.7507257857332581</v>
+        <v>4.3332314507797411</v>
       </c>
       <c r="C18">
         <v>338.16769933532214</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>4.5209093732966776</v>
+        <v>3.8993588024293264</v>
       </c>
       <c r="B19">
-        <v>3.2526085193926879</v>
+        <v>2.840092991707214</v>
       </c>
       <c r="C19">
         <v>338.16769933532214</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>5.5980963148755736</v>
+        <v>4.9865652768745825</v>
       </c>
       <c r="B20">
-        <v>1.7215040060170079</v>
+        <v>1.3159617206275029</v>
       </c>
       <c r="C20">
         <v>338.16769933532214</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>6.6310296803127056</v>
+        <v>6.0319155129797108</v>
       </c>
       <c r="B21">
-        <v>0.16000886321599966</v>
+        <v>-0.23706494519024632</v>
       </c>
       <c r="C21">
         <v>338.16769933532214</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>7.62280403887707</v>
+        <v>7.0378934085479905</v>
       </c>
       <c r="B22">
-        <v>-1.4297517495072092</v>
+        <v>-1.8172722504225498</v>
       </c>
       <c r="C22">
         <v>338.16769933532214</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8.5737678887473656</v>
+        <v>8.004765651374445</v>
       </c>
       <c r="B23">
-        <v>-3.04753850507609</v>
+        <v>-3.4244760875285909</v>
       </c>
       <c r="C23">
         <v>338.16769933532214</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>9.48358321032971</v>
+        <v>8.93224462675202</v>
       </c>
       <c r="B24">
-        <v>-4.6935835345207444</v>
+        <v>-5.0588750109132</v>
       </c>
       <c r="C24">
         <v>338.16769933532214</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>10.351911984030235</v>
+        <v>9.8200427199736779</v>
       </c>
       <c r="B25">
-        <v>-6.3681189688712987</v>
+        <v>-6.72066757498123</v>
       </c>
       <c r="C25">
         <v>338.16769933532214</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>11.17827786433</v>
+        <v>10.667755752051848</v>
       </c>
       <c r="B26">
-        <v>-8.07147193288027</v>
+        <v>-8.41013280412314</v>
       </c>
       <c r="C26">
         <v>338.16769933532214</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>11.961651202009868</v>
+        <v>11.47451328687692</v>
       </c>
       <c r="B27">
-        <v>-9.8043495261899025</v>
+        <v>-10.127871602671943</v>
       </c>
       <c r="C27">
         <v>338.16769933532214</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>12.700864021925646</v>
+        <v>12.239328324058766</v>
       </c>
       <c r="B28">
-        <v>-11.567553842164845</v>
+        <v>-11.874565344946275</v>
       </c>
       <c r="C28">
         <v>338.16769933532214</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>13.394748348933135</v>
+        <v>12.961213863207242</v>
       </c>
       <c r="B29">
-        <v>-13.361886974169732</v>
+        <v>-13.650895405264754</v>
       </c>
       <c r="C29">
         <v>338.16769933532214</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>14.042590514412423</v>
+        <v>13.639538661357072</v>
       </c>
       <c r="B30">
-        <v>-15.187839025840287</v>
+        <v>-15.457297561312647</v>
       </c>
       <c r="C30">
         <v>338.16769933532214</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>14.645494075840714</v>
+        <v>14.275094505242336</v>
       </c>
       <c r="B31">
-        <v>-17.044652141896456</v>
+        <v>-17.293225204241725</v>
       </c>
       <c r="C31">
         <v>338.16769933532214</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>15.205016897219494</v>
+        <v>14.869028939021973</v>
       </c>
       <c r="B32">
-        <v>-18.9312564773293</v>
+        <v>-19.157886128570418</v>
       </c>
       <c r="C32">
         <v>338.16769933532214</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>15.722716842550257</v>
+        <v>15.42248950685492</v>
       </c>
       <c r="B33">
-        <v>-20.846582187129837</v>
+        <v>-21.050488128817126</v>
       </c>
       <c r="C33">
         <v>338.16769933532214</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>16.199313618711145</v>
+        <v>15.935944794344213</v>
       </c>
       <c r="B34">
-        <v>-22.790135020958644</v>
+        <v>-22.970707717575781</v>
       </c>
       <c r="C34">
         <v>338.16769933532214</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>16.632174304087002</v>
+        <v>16.407147552869311</v>
       </c>
       <c r="B35">
-        <v>-24.763723107154465</v>
+        <v>-24.92009627974241</v>
       </c>
       <c r="C35">
         <v>338.16769933532214</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>17.01782781993931</v>
+        <v>16.833171575253768</v>
       </c>
       <c r="B36">
-        <v>-26.769730168725562</v>
+        <v>-26.90067391828854</v>
       </c>
       <c r="C36">
         <v>338.16769933532214</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>17.35280308752958</v>
+        <v>17.211090654321147</v>
       </c>
       <c r="B37">
-        <v>-28.81053992868026</v>
+        <v>-28.914460736185742</v>
       </c>
       <c r="C37">
         <v>338.16769933532214</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>17.631632357274675</v>
+        <v>17.536372366958407</v>
       </c>
       <c r="B38">
-        <v>-30.889907300538702</v>
+        <v>-30.964585685297909</v>
       </c>
       <c r="C38">
         <v>338.16769933532214</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>17.840861196213019</v>
+        <v>17.798059426306132</v>
       </c>
       <c r="B39">
-        <v>-33.017071959868694</v>
+        <v>-33.058613113058485</v>
       </c>
       <c r="C39">
         <v>338.16769933532214</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>17.965038500538391</v>
+        <v>17.983588329568288</v>
       </c>
       <c r="B40">
-        <v>-35.2026447727499</v>
+        <v>-35.205216215793278</v>
       </c>
       <c r="C40">
         <v>338.16769933532214</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>17.988713166444573</v>
+        <v>18.080395573948856</v>
       </c>
       <c r="B41">
-        <v>-37.457236605261969</v>
+        <v>-37.41306818982806</v>
       </c>
       <c r="C41">
         <v>338.16769933532214</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>17.988713166444573</v>
+        <v>18.080395573948856</v>
       </c>
       <c r="B42">
-        <v>-37.457236605261969</v>
+        <v>-37.41306818982806</v>
       </c>
       <c r="C42">
         <v>338.16769933532214</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>17.287788026403287</v>
+        <v>17.442700822704232</v>
       </c>
       <c r="B43">
-        <v>-35.667738669831436</v>
+        <v>-35.578617138559096</v>
       </c>
       <c r="C43">
         <v>338.16769933532214</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>16.602672660655063</v>
+        <v>16.80917756412526</v>
       </c>
       <c r="B44">
-        <v>-33.867383555530196</v>
+        <v>-33.741286303248337</v>
       </c>
       <c r="C44">
         <v>338.16769933532214</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>15.920154200996375</v>
+        <v>16.169496759844414</v>
       </c>
       <c r="B45">
-        <v>-32.065245046134145</v>
+        <v>-31.90820632087442</v>
       </c>
       <c r="C45">
         <v>338.16769933532214</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>15.227019779223694</v>
+        <v>15.513329371494171</v>
       </c>
       <c r="B46">
-        <v>-30.27039692541916</v>
+        <v>-30.086507828415968</v>
       </c>
       <c r="C46">
         <v>338.16769933532214</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>14.511937296769791</v>
+        <v>14.831836870715733</v>
       </c>
       <c r="B47">
-        <v>-28.490621380457817</v>
+        <v>-28.282292491382304</v>
       </c>
       <c r="C47">
         <v>338.16769933532214</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>13.77109773361275</v>
+        <v>14.1221427691853</v>
       </c>
       <c r="B48">
-        <v>-26.728534211509771</v>
+        <v>-26.497546089405631</v>
       </c>
       <c r="C48">
         <v>338.16769933532214</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>13.002572839366948</v>
+        <v>13.382861088587804</v>
       </c>
       <c r="B49">
-        <v>-24.985459622131334</v>
+        <v>-24.733225430648833</v>
       </c>
       <c r="C49">
         <v>338.16769933532214</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>12.204434363646785</v>
+        <v>12.612605850608183</v>
       </c>
       <c r="B50">
-        <v>-23.262721815878887</v>
+        <v>-22.990287323274821</v>
       </c>
       <c r="C50">
         <v>338.16769933532214</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>11.375496425625761</v>
+        <v>11.810574409314281</v>
       </c>
       <c r="B51">
-        <v>-21.561135182636409</v>
+        <v>-21.269285872763781</v>
       </c>
       <c r="C51">
         <v>338.16769933532214</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>10.517542622713872</v>
+        <v>10.978297448305588</v>
       </c>
       <c r="B52">
-        <v>-19.879474857598481</v>
+        <v>-19.569164373865071</v>
       </c>
       <c r="C52">
         <v>338.16769933532214</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>9.633098921880217</v>
+        <v>10.117888983564505</v>
       </c>
       <c r="B53">
-        <v>-18.216006162287293</v>
+        <v>-17.888463418645344</v>
       </c>
       <c r="C53">
         <v>338.16769933532214</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>8.7246912900938973</v>
+        <v>9.2314630310734156</v>
       </c>
       <c r="B54">
-        <v>-16.568994418225042</v>
+        <v>-16.225723599171232</v>
       </c>
       <c r="C54">
         <v>338.16769933532214</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>7.794320514081182</v>
+        <v>8.3207070950855346</v>
       </c>
       <c r="B55">
-        <v>-14.937065608365931</v>
+        <v>-14.579779949276363</v>
       </c>
       <c r="C55">
         <v>338.16769933532214</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>6.8418866595969439</v>
+        <v>7.3856026329372613</v>
       </c>
       <c r="B56">
-        <v>-13.320288361392077</v>
+        <v>-12.950645269862227</v>
       </c>
       <c r="C56">
         <v>338.16769933532214</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>5.8667646121532329</v>
+        <v>6.4257045902358181</v>
       </c>
       <c r="B57">
-        <v>-11.719091967417612</v>
+        <v>-11.338626803597293</v>
       </c>
       <c r="C57">
         <v>338.16769933532214</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>4.8683292572620891</v>
+        <v>5.4405679125884125</v>
       </c>
       <c r="B58">
-        <v>-10.133905716556654</v>
+        <v>-9.7440317931500324</v>
       </c>
       <c r="C58">
         <v>338.16769933532214</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>3.8460328036647398</v>
+        <v>4.42980320996956</v>
       </c>
       <c r="B59">
-        <v>-8.56510579809373</v>
+        <v>-8.1671290533719123</v>
       </c>
       <c r="C59">
         <v>338.16769933532214</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2.7996367530192332</v>
+        <v>3.393243749823049</v>
       </c>
       <c r="B60">
-        <v>-7.0128559979951248</v>
+        <v>-6.6080336878465156</v>
       </c>
       <c r="C60">
         <v>338.16769933532214</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.7289799302128008</v>
+        <v>2.3307784639599669</v>
       </c>
       <c r="B61">
-        <v>-5.4772670013975242</v>
+        <v>-5.0668223723404253</v>
       </c>
       <c r="C61">
         <v>338.16769933532214</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>0.63390116013268516</v>
+        <v>1.2422962841914111</v>
       </c>
       <c r="B62">
-        <v>-3.9584494934376382</v>
+        <v>-3.5435717826202424</v>
       </c>
       <c r="C62">
         <v>338.16769933532214</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-0.48513445253478193</v>
+        <v>0.12818030835123895</v>
       </c>
       <c r="B63">
-        <v>-2.4560840688741483</v>
+        <v>-2.0380174476400281</v>
       </c>
       <c r="C63">
         <v>338.16769933532214</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.6251566839068854</v>
+        <v>-1.009209701635621</v>
       </c>
       <c r="B64">
-        <v>-0.96813096095372719</v>
+        <v>-0.54853030910375122</v>
       </c>
       <c r="C64">
         <v>338.16769933532214</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.78256903030181</v>
+        <v>-2.1670198178214743</v>
       </c>
       <c r="B65">
-        <v>0.50787968745496137</v>
+        <v>0.92685983809714156</v>
       </c>
       <c r="C65">
         <v>338.16769933532214</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-3.9537749880377482</v>
+        <v>-3.3423961122586259</v>
       </c>
       <c r="B66">
-        <v>1.9744177334832529</v>
+        <v>2.3901231990712084</v>
       </c>
       <c r="C66">
         <v>338.16769933532214</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-5.1399676677767063</v>
+        <v>-4.5363149003126759</v>
       </c>
       <c r="B67">
-        <v>3.43066382224158</v>
+        <v>3.8405857758913355</v>
       </c>
       <c r="C67">
         <v>338.16769933532214</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-6.3614986375559823</v>
+        <v>-5.7650734706024185</v>
       </c>
       <c r="B68">
-        <v>4.8626417507567679</v>
+        <v>5.2669967584877488</v>
       </c>
       <c r="C68">
         <v>338.16769933532214</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-7.634216556615482</v>
+        <v>-7.0413803388427088</v>
       </c>
       <c r="B69">
-        <v>6.2594676363725332</v>
+        <v>6.6605828410719345</v>
       </c>
       <c r="C69">
         <v>338.16769933532214</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-8.9367999916302079</v>
+        <v>-8.3482679558794057</v>
       </c>
       <c r="B70">
-        <v>7.63578372578371</v>
+        <v>8.033057547123029</v>
       </c>
       <c r="C70">
         <v>338.16769933532214</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-10.246006455705263</v>
+        <v>-9.6672407826772986</v>
       </c>
       <c r="B71">
-        <v>9.0075515269119126</v>
+        <v>9.3971892457661532</v>
       </c>
       <c r="C71">
         <v>338.16769933532214</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-11.568079340231009</v>
+        <v>-11.003367385545833</v>
       </c>
       <c r="B72">
-        <v>10.370483463234638</v>
+        <v>10.749478859442606</v>
       </c>
       <c r="C72">
         <v>338.16769933532214</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-12.913213864146066</v>
+        <v>-12.364880225508674</v>
       </c>
       <c r="B73">
-        <v>11.717578086559746</v>
+        <v>12.084243120367749</v>
       </c>
       <c r="C73">
         <v>338.16769933532214</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-14.277926678296838</v>
+        <v>-13.749103237101762</v>
       </c>
       <c r="B74">
-        <v>13.051227546460559</v>
+        <v>13.403329446536976</v>
       </c>
       <c r="C74">
         <v>338.16769933532214</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-15.655262202194029</v>
+        <v>-15.150595776280809</v>
       </c>
       <c r="B75">
-        <v>14.376208507051452</v>
+        <v>14.710493778845205</v>
       </c>
       <c r="C75">
         <v>338.16769933532214</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-17.038054498097683</v>
+        <v>-16.563767411168357</v>
       </c>
       <c r="B76">
-        <v>15.697442092845424</v>
+        <v>16.009595464005397</v>
       </c>
       <c r="C76">
         <v>338.16769933532214</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-18.419768145771908</v>
+        <v>-17.983541457663918</v>
       </c>
       <c r="B77">
-        <v>17.019416427782836</v>
+        <v>17.304139183681777</v>
       </c>
       <c r="C77">
         <v>338.16769933532214</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-19.796600152247649</v>
+        <v>-19.407046010608024</v>
       </c>
       <c r="B78">
-        <v>18.344743173114722</v>
+        <v>18.596107553525535</v>
       </c>
       <c r="C78">
         <v>338.16769933532214</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-21.161545479239908</v>
+        <v>-20.828862710535084</v>
       </c>
       <c r="B79">
-        <v>19.678232957522205</v>
+        <v>19.889241130304296</v>
       </c>
       <c r="C79">
         <v>338.16769933532214</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-22.501774634481389</v>
+        <v>-22.238945136349219</v>
       </c>
       <c r="B80">
-        <v>21.028696285809723</v>
+        <v>21.190475446564289</v>
       </c>
       <c r="C80">
         <v>338.16769933532214</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-23.784442503802065</v>
+        <v>-23.611281742306129</v>
       </c>
       <c r="B81">
-        <v>22.418689158648871</v>
+        <v>22.517767535995926</v>
       </c>
       <c r="C81">
         <v>338.16769933532214</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-24.399701373012373</v>
+        <v>-24.459060444860274</v>
       </c>
       <c r="B82">
-        <v>24.267017410588384</v>
+        <v>24.207187429617946</v>
       </c>
       <c r="C82">
         <v>338.16769933532214</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-35.316038661929653</v>
+        <v>-35.029782607196793</v>
       </c>
       <c r="B1">
-        <v>17.415380190787396</v>
+        <v>17.984225989825436</v>
       </c>
       <c r="C1">
         <v>410.1621514722421</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-32.954985761151825</v>
+        <v>-32.755237845847823</v>
       </c>
       <c r="B2">
-        <v>17.162320632611884</v>
+        <v>17.554527995661036</v>
       </c>
       <c r="C2">
         <v>410.1621514722421</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-30.8004573758842</v>
+        <v>-30.641997984664236</v>
       </c>
       <c r="B3">
-        <v>16.54771451646555</v>
+        <v>16.852758411026429</v>
       </c>
       <c r="C3">
         <v>410.1621514722421</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-28.681494092815669</v>
+        <v>-28.558224305193431</v>
       </c>
       <c r="B4">
-        <v>15.870847315952535</v>
+        <v>16.10128847063411</v>
       </c>
       <c r="C4">
         <v>410.1621514722421</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-26.588577687982124</v>
+        <v>-26.4965713783175</v>
       </c>
       <c r="B5">
-        <v>15.148381852451326</v>
+        <v>15.312507646724203</v>
       </c>
       <c r="C5">
         <v>410.1621514722421</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-24.517818793302656</v>
+        <v>-24.45403470618437</v>
       </c>
       <c r="B6">
-        <v>14.387126943011364</v>
+        <v>14.491483600033263</v>
       </c>
       <c r="C6">
         <v>410.1621514722421</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-22.466992083048567</v>
+        <v>-22.4288934077408</v>
       </c>
       <c r="B7">
-        <v>13.590978293939408</v>
+        <v>13.641118925861749</v>
       </c>
       <c r="C7">
         <v>410.1621514722421</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-20.434783979100263</v>
+        <v>-20.420129889919878</v>
       </c>
       <c r="B8">
-        <v>12.762235485247022</v>
+        <v>12.76312998970063</v>
       </c>
       <c r="C8">
         <v>410.1621514722421</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-18.41914988016315</v>
+        <v>-18.42616329833913</v>
       </c>
       <c r="B9">
-        <v>11.904477842897798</v>
+        <v>11.860183205066786</v>
       </c>
       <c r="C9">
         <v>410.1621514722421</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-16.417883938868552</v>
+        <v>-16.445288657900015</v>
       </c>
       <c r="B10">
-        <v>11.02156697393429</v>
+        <v>10.935154338823462</v>
       </c>
       <c r="C10">
         <v>410.1621514722421</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-14.428866346726466</v>
+        <v>-14.475867771955187</v>
       </c>
       <c r="B11">
-        <v>10.117213863762878</v>
+        <v>9.9908065231934664</v>
       </c>
       <c r="C11">
         <v>410.1621514722421</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-12.450961363779518</v>
+        <v>-12.517021505906918</v>
       </c>
       <c r="B12">
-        <v>9.1934067648257471</v>
+        <v>9.0286225869563115</v>
       </c>
       <c r="C12">
         <v>410.1621514722421</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-10.486883485322268</v>
+        <v>-10.570840194904649</v>
       </c>
       <c r="B13">
-        <v>8.245393619344453</v>
+        <v>8.0450767797588565</v>
       </c>
       <c r="C13">
         <v>410.1621514722421</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-8.53825346633315</v>
+        <v>-8.6385709696779287</v>
       </c>
       <c r="B14">
-        <v>7.2703370964465766</v>
+        <v>7.0380655769049136</v>
       </c>
       <c r="C14">
         <v>410.1621514722421</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-6.5984668652742258</v>
+        <v>-6.7151186735295916</v>
       </c>
       <c r="B15">
-        <v>6.2797990831045132</v>
+        <v>6.0161829354588283</v>
       </c>
       <c r="C15">
         <v>410.1621514722421</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-4.6614661311685577</v>
+        <v>-4.7958100647587623</v>
       </c>
       <c r="B16">
-        <v>5.284384067119813</v>
+        <v>4.9873111720824621</v>
       </c>
       <c r="C16">
         <v>410.1621514722421</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.731606471799485</v>
+        <v>-2.8840018490763342</v>
       </c>
       <c r="B17">
-        <v>4.2764677217658047</v>
+        <v>3.9457885600671423</v>
       </c>
       <c r="C17">
         <v>410.1621514722421</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-0.81451415270394856</v>
+        <v>-0.98403113619234428</v>
       </c>
       <c r="B18">
-        <v>3.2462005774330929</v>
+        <v>2.884299733694621</v>
       </c>
       <c r="C18">
         <v>410.1621514722421</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>1.0895130883269903</v>
+        <v>0.90387329559837948</v>
       </c>
       <c r="B19">
-        <v>2.1930614075096155</v>
+        <v>1.8024588145788834</v>
       </c>
       <c r="C19">
         <v>410.1621514722421</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.9815096454387797</v>
+        <v>2.7805097508548511</v>
       </c>
       <c r="B20">
-        <v>1.1188610461326147</v>
+        <v>0.70161229616694309</v>
       </c>
       <c r="C20">
         <v>410.1621514722421</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>4.8625099127768463</v>
+        <v>4.6466765341360619</v>
       </c>
       <c r="B21">
-        <v>0.025410327439348655</v>
+        <v>-0.41689332809416879</v>
       </c>
       <c r="C21">
         <v>410.1621514722421</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>6.7333638449769619</v>
+        <v>6.5030295106258889</v>
       </c>
       <c r="B22">
-        <v>-1.0858027984726537</v>
+        <v>-1.5519518160287433</v>
       </c>
       <c r="C22">
         <v>410.1621514722421</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>8.5941836386362773</v>
+        <v>8.3496547880077365</v>
       </c>
       <c r="B23">
-        <v>-2.2145819176647739</v>
+        <v>-2.7034179305463431</v>
       </c>
       <c r="C23">
         <v>410.1621514722421</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>10.444897050842272</v>
+        <v>10.186496034589872</v>
       </c>
       <c r="B24">
-        <v>-3.3610535002381052</v>
+        <v>-3.8713866858278361</v>
       </c>
       <c r="C24">
         <v>410.1621514722421</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>12.285431838682433</v>
+        <v>12.01349691868058</v>
       </c>
       <c r="B25">
-        <v>-4.5253440162937553</v>
+        <v>-5.0559530960541021</v>
       </c>
       <c r="C25">
         <v>410.1621514722421</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>14.115684801205806</v>
+        <v>13.830577031161026</v>
       </c>
       <c r="B26">
-        <v>-5.70763413178561</v>
+        <v>-6.2572527865956342</v>
       </c>
       <c r="C26">
         <v>410.1621514722421</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>15.935428905307681</v>
+        <v>15.637559653203969</v>
       </c>
       <c r="B27">
-        <v>-6.9083212960787259</v>
+        <v>-7.4755838275814206</v>
       </c>
       <c r="C27">
         <v>410.1621514722421</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>17.7444061598449</v>
+        <v>17.434243988555039</v>
       </c>
       <c r="B28">
-        <v>-8.1278571543909415</v>
+        <v>-8.71128490033006</v>
       </c>
       <c r="C28">
         <v>410.1621514722421</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>19.542358573674292</v>
+        <v>19.220429240959874</v>
       </c>
       <c r="B29">
-        <v>-9.3666933519400857</v>
+        <v>-9.9646946861601489</v>
       </c>
       <c r="C29">
         <v>410.1621514722421</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>21.329164340279569</v>
+        <v>20.996019422009184</v>
       </c>
       <c r="B30">
-        <v>-10.625043126009855</v>
+        <v>-11.235975087897673</v>
       </c>
       <c r="C30">
         <v>410.1621514722421</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>23.105246391651921</v>
+        <v>22.761337774673976</v>
       </c>
       <c r="B31">
-        <v>-11.902166082147346</v>
+        <v>-12.524580894398129</v>
       </c>
       <c r="C31">
         <v>410.1621514722421</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>24.871163844409427</v>
+        <v>24.516812349770358</v>
       </c>
       <c r="B32">
-        <v>-13.197083417965523</v>
+        <v>-13.829790116024421</v>
       </c>
       <c r="C32">
         <v>410.1621514722421</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>26.627475815170122</v>
+        <v>26.262871198114389</v>
       </c>
       <c r="B33">
-        <v>-14.50881633107733</v>
+        <v>-15.150880763139419</v>
       </c>
       <c r="C33">
         <v>410.1621514722421</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>28.374519494602019</v>
+        <v>27.999771013723826</v>
       </c>
       <c r="B34">
-        <v>-15.83677452775863</v>
+        <v>-16.487419872146894</v>
       </c>
       <c r="C34">
         <v>410.1621514722421</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>30.111744369572776</v>
+        <v>29.727083063422956</v>
       </c>
       <c r="B35">
-        <v>-17.181921748936837</v>
+        <v>-17.840130583614052</v>
       </c>
       <c r="C35">
         <v>410.1621514722421</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>31.838378000999949</v>
+        <v>31.444207257237704</v>
       </c>
       <c r="B36">
-        <v>-18.545610244202251</v>
+        <v>-19.210025064148972</v>
       </c>
       <c r="C36">
         <v>410.1621514722421</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>33.553647949801153</v>
+        <v>33.150543505194022</v>
       </c>
       <c r="B37">
-        <v>-19.929192263145211</v>
+        <v>-20.598115480359752</v>
       </c>
       <c r="C37">
         <v>410.1621514722421</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>35.256238656907016</v>
+        <v>34.84507269377729</v>
       </c>
       <c r="B38">
-        <v>-21.334970853673436</v>
+        <v>-22.006120762263468</v>
       </c>
       <c r="C38">
         <v>410.1621514722421</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>36.94266208330032</v>
+        <v>36.525099615310552</v>
       </c>
       <c r="B39">
-        <v>-22.769052256964265</v>
+        <v>-23.438586893513165</v>
       </c>
       <c r="C39">
         <v>410.1621514722421</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>38.608887069976916</v>
+        <v>38.187510038576335</v>
       </c>
       <c r="B40">
-        <v>-24.238493512512445</v>
+        <v>-24.9007666211709</v>
       </c>
       <c r="C40">
         <v>410.1621514722421</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>40.250882457932612</v>
+        <v>39.829189732357129</v>
       </c>
       <c r="B41">
-        <v>-25.750351659812718</v>
+        <v>-26.3979126922987</v>
       </c>
       <c r="C41">
         <v>410.1621514722421</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>40.250882457932612</v>
+        <v>39.829189732357129</v>
       </c>
       <c r="B42">
-        <v>-25.750351659812718</v>
+        <v>-26.3979126922987</v>
       </c>
       <c r="C42">
         <v>410.1621514722421</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>38.419437960687063</v>
+        <v>38.04141921117867</v>
       </c>
       <c r="B43">
-        <v>-24.570147472359185</v>
+        <v>-25.147176765701168</v>
       </c>
       <c r="C43">
         <v>410.1621514722421</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>36.596300250931108</v>
+        <v>36.258007904721531</v>
       </c>
       <c r="B44">
-        <v>-23.375401232030036</v>
+        <v>-23.8890881890526</v>
       </c>
       <c r="C44">
         <v>410.1621514722421</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>34.777482237149577</v>
+        <v>34.475886891075504</v>
       </c>
       <c r="B45">
-        <v>-22.173092832762165</v>
+        <v>-22.628823286595416</v>
       </c>
       <c r="C45">
         <v>410.1621514722421</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>32.958996827827285</v>
+        <v>32.691987248330314</v>
       </c>
       <c r="B46">
-        <v>-20.970202168492435</v>
+        <v>-21.371558382572022</v>
       </c>
       <c r="C46">
         <v>410.1621514722421</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>31.137398458388915</v>
+        <v>30.903657440177277</v>
       </c>
       <c r="B47">
-        <v>-19.772761123665191</v>
+        <v>-20.121765800513611</v>
       </c>
       <c r="C47">
         <v>410.1621514722421</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>29.311407672018444</v>
+        <v>29.109915472713688</v>
       </c>
       <c r="B48">
-        <v>-18.583009544754631</v>
+        <v>-18.881101861106423</v>
       </c>
       <c r="C48">
         <v>410.1621514722421</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>27.480286538839671</v>
+        <v>27.310196737638343</v>
       </c>
       <c r="B49">
-        <v>-17.402239268742406</v>
+        <v>-17.650518884325475</v>
       </c>
       <c r="C49">
         <v>410.1621514722421</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>25.643297128976442</v>
+        <v>25.503936626650066</v>
       </c>
       <c r="B50">
-        <v>-16.23174213261019</v>
+        <v>-16.430969190145792</v>
       </c>
       <c r="C50">
         <v>410.1621514722421</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>23.799921711611841</v>
+        <v>23.690740112691582</v>
       </c>
       <c r="B51">
-        <v>-15.072424487811484</v>
+        <v>-15.223119067314014</v>
       </c>
       <c r="C51">
         <v>410.1621514722421</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>21.950523352165945</v>
+        <v>21.870890493681134</v>
       </c>
       <c r="B52">
-        <v>-13.923650743687063</v>
+        <v>-14.026490679663208</v>
       </c>
       <c r="C52">
         <v>410.1621514722421</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>20.095685315118128</v>
+        <v>20.044840648780898</v>
       </c>
       <c r="B53">
-        <v>-12.784399824049563</v>
+        <v>-12.840320159798091</v>
       </c>
       <c r="C53">
         <v>410.1621514722421</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>18.235990864947727</v>
+        <v>18.21304345715302</v>
       </c>
       <c r="B54">
-        <v>-11.653650652711596</v>
+        <v>-11.663843640323345</v>
       </c>
       <c r="C54">
         <v>410.1621514722421</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>16.371885456274924</v>
+        <v>16.37584531908335</v>
       </c>
       <c r="B55">
-        <v>-10.530623406588939</v>
+        <v>-10.496476850850321</v>
       </c>
       <c r="C55">
         <v>410.1621514722421</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>14.503263304283125</v>
+        <v>14.53316671935251</v>
       </c>
       <c r="B56">
-        <v>-9.41550327500996</v>
+        <v>-9.33835390901699</v>
       </c>
       <c r="C56">
         <v>410.1621514722421</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>12.629880814296577</v>
+        <v>12.684821663864824</v>
       </c>
       <c r="B57">
-        <v>-8.3087167004062</v>
+        <v>-8.1897885294679735</v>
       </c>
       <c r="C57">
         <v>410.1621514722421</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>10.751494391639509</v>
+        <v>10.830624158524607</v>
       </c>
       <c r="B58">
-        <v>-7.2106901252091795</v>
+        <v>-7.051094426847893</v>
       </c>
       <c r="C58">
         <v>410.1621514722421</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>8.8678898077196475</v>
+        <v>8.9704106498471816</v>
       </c>
       <c r="B59">
-        <v>-6.1217985829104835</v>
+        <v>-5.9225474654153958</v>
       </c>
       <c r="C59">
         <v>410.1621514722421</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>6.9789702982787762</v>
+        <v>7.1041073467919276</v>
       </c>
       <c r="B60">
-        <v>-5.042211471241953</v>
+        <v>-4.8042721078852777</v>
       </c>
       <c r="C60">
         <v>410.1621514722421</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>5.08466846514217</v>
+        <v>5.2316628989292351</v>
       </c>
       <c r="B61">
-        <v>-3.9720467789954816</v>
+        <v>-3.6963549665863633</v>
       </c>
       <c r="C61">
         <v>410.1621514722421</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>3.184916910135124</v>
+        <v>3.3530259558295077</v>
       </c>
       <c r="B62">
-        <v>-2.9114224949629777</v>
+        <v>-2.5988826538474865</v>
       </c>
       <c r="C62">
         <v>410.1621514722421</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.2798310279933574</v>
+        <v>1.468285913438006</v>
       </c>
       <c r="B63">
-        <v>-1.8601366064709932</v>
+        <v>-1.511704386295136</v>
       </c>
       <c r="C63">
         <v>410.1621514722421</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.62974261490562922</v>
+        <v>-0.42190484680051077</v>
       </c>
       <c r="B64">
-        <v>-0.81670709498471816</v>
+        <v>-0.43371979774646935</v>
       </c>
       <c r="C64">
         <v>410.1621514722421</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.5427746592738867</v>
+        <v>-2.3167531970664035</v>
       </c>
       <c r="B65">
-        <v>0.22066805949599638</v>
+        <v>0.63640887368368815</v>
       </c>
       <c r="C65">
         <v>410.1621514722421</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-4.4582357458234894</v>
+        <v>-4.2154660095400578</v>
       </c>
       <c r="B66">
-        <v>1.2537908769713138</v>
+        <v>1.7000193898805247</v>
       </c>
       <c r="C66">
         <v>410.1621514722421</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.3764299748009536</v>
+        <v>-6.1182786042652371</v>
       </c>
       <c r="B67">
-        <v>2.282128992568508</v>
+        <v>2.7567148385461677</v>
       </c>
       <c r="C67">
         <v>410.1621514722421</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-8.3029952845907236</v>
+        <v>-8.02954009273938</v>
       </c>
       <c r="B68">
-        <v>3.2958125019233919</v>
+        <v>3.7991596106505994</v>
       </c>
       <c r="C68">
         <v>410.1621514722421</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-10.242300477319555</v>
+        <v>-9.9526211581042983</v>
       </c>
       <c r="B69">
-        <v>4.2871932797396584</v>
+        <v>4.8216684038724358</v>
       </c>
       <c r="C69">
         <v>410.1621514722421</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-12.188303971945523</v>
+        <v>-11.882864978625602</v>
       </c>
       <c r="B70">
-        <v>5.2668478564839605</v>
+        <v>5.8320958394569633</v>
       </c>
       <c r="C70">
         <v>410.1621514722421</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-14.134418764131967</v>
+        <v>-13.815194326186319</v>
       </c>
       <c r="B71">
-        <v>6.2463075931638805</v>
+        <v>6.8390056344862469</v>
       </c>
       <c r="C71">
         <v>410.1621514722421</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-16.08228653953185</v>
+        <v>-15.75087785201525</v>
       </c>
       <c r="B72">
-        <v>7.2226985171876725</v>
+        <v>7.84025796582276</v>
       </c>
       <c r="C72">
         <v>410.1621514722421</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-18.034644412164489</v>
+        <v>-17.692029147380431</v>
       </c>
       <c r="B73">
-        <v>8.1912289739180419</v>
+        <v>8.8322878572177217</v>
       </c>
       <c r="C73">
         <v>410.1621514722421</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-19.990382519524992</v>
+        <v>-19.637795684361119</v>
       </c>
       <c r="B74">
-        <v>9.1538419141348122</v>
+        <v>9.8165332601969642</v>
       </c>
       <c r="C74">
         <v>410.1621514722421</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-21.947408583371267</v>
+        <v>-21.586567572358046</v>
       </c>
       <c r="B75">
-        <v>10.114200128160389</v>
+        <v>10.795709563415002</v>
       </c>
       <c r="C75">
         <v>410.1621514722421</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-23.903547639036535</v>
+        <v>-23.53667158924662</v>
       </c>
       <c r="B76">
-        <v>11.076111159070392</v>
+        <v>11.772638976266483</v>
       </c>
       <c r="C76">
         <v>410.1621514722421</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-25.856787693427471</v>
+        <v>-25.486560407742086</v>
       </c>
       <c r="B77">
-        <v>12.043097248162718</v>
+        <v>12.749931362400352</v>
       </c>
       <c r="C77">
         <v>410.1621514722421</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-27.805851326169048</v>
+        <v>-27.435253611444431</v>
       </c>
       <c r="B78">
-        <v>13.017394676871209</v>
+        <v>13.729240381742638</v>
       </c>
       <c r="C78">
         <v>410.1621514722421</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-29.748550984162506</v>
+        <v>-29.381069156360009</v>
       </c>
       <c r="B79">
-        <v>14.002833025869538</v>
+        <v>14.713403123458779</v>
       </c>
       <c r="C79">
         <v>410.1621514722421</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-31.681038305636442</v>
+        <v>-31.321044706500739</v>
       </c>
       <c r="B80">
-        <v>15.006149325620356</v>
+        <v>15.707416134231252</v>
       </c>
       <c r="C80">
         <v>410.1621514722421</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-33.593838592540713</v>
+        <v>-33.2478795852194</v>
       </c>
       <c r="B81">
-        <v>16.043930200037924</v>
+        <v>16.723593402691989</v>
       </c>
       <c r="C81">
         <v>410.1621514722421</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-35.316038661929653</v>
+        <v>-35.029782607196793</v>
       </c>
       <c r="B82">
-        <v>17.415380190787396</v>
+        <v>17.984225989825436</v>
       </c>
       <c r="C82">
         <v>410.1621514722421</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-41.465147778311618</v>
+        <v>-41.096278841482686</v>
       </c>
       <c r="B1">
-        <v>14.664112268594032</v>
+        <v>15.66813755001701</v>
       </c>
       <c r="C1">
         <v>471.28397822006644</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-38.939854427263668</v>
+        <v>-38.646223413393564</v>
       </c>
       <c r="B2">
-        <v>14.445430657212297</v>
+        <v>15.221844481190527</v>
       </c>
       <c r="C2">
         <v>471.28397822006644</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-36.539127008466004</v>
+        <v>-36.285509069605027</v>
       </c>
       <c r="B3">
-        <v>13.90552956662741</v>
+        <v>14.560810256284299</v>
       </c>
       <c r="C3">
         <v>471.28397822006644</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-34.158436333235834</v>
+        <v>-33.940099503064644</v>
       </c>
       <c r="B4">
-        <v>13.313959514734968</v>
+        <v>13.862989310178719</v>
       </c>
       <c r="C4">
         <v>471.28397822006644</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-31.791973258967815</v>
+        <v>-31.6058794974743</v>
       </c>
       <c r="B5">
-        <v>12.685700598649808</v>
+        <v>13.138273019414559</v>
       </c>
       <c r="C5">
         <v>471.28397822006644</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-29.437370013921161</v>
+        <v>-29.281171317780835</v>
       </c>
       <c r="B6">
-        <v>12.026858616255048</v>
+        <v>12.390694005352193</v>
       </c>
       <c r="C6">
         <v>471.28397822006644</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-27.093275542677546</v>
+        <v>-26.965017397426102</v>
       </c>
       <c r="B7">
-        <v>11.340917548363201</v>
+        <v>11.622553884894199</v>
       </c>
       <c r="C7">
         <v>471.28397822006644</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-24.758895901625809</v>
+        <v>-24.656854785353147</v>
       </c>
       <c r="B8">
-        <v>10.629924745712025</v>
+        <v>10.835205773035023</v>
       </c>
       <c r="C8">
         <v>471.28397822006644</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-22.432989209338963</v>
+        <v>-22.355803325541974</v>
       </c>
       <c r="B9">
-        <v>9.8970826609946663</v>
+        <v>10.030765221905508</v>
       </c>
       <c r="C9">
         <v>471.28397822006644</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-20.114214536579247</v>
+        <v>-20.060912737531869</v>
       </c>
       <c r="B10">
-        <v>9.1458491625353329</v>
+        <v>9.2115163354689127</v>
       </c>
       <c r="C10">
         <v>471.28397822006644</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-17.80128270068159</v>
+        <v>-17.771269448062295</v>
       </c>
       <c r="B11">
-        <v>8.379548679227133</v>
+        <v>8.3796549878817732</v>
       </c>
       <c r="C11">
         <v>471.28397822006644</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-15.493505847158048</v>
+        <v>-15.486385818172316</v>
       </c>
       <c r="B12">
-        <v>7.5999549886703424</v>
+        <v>7.5363532732040426</v>
       </c>
       <c r="C12">
         <v>471.28397822006644</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-13.192549687656495</v>
+        <v>-13.207441238899316</v>
       </c>
       <c r="B13">
-        <v>6.8027727027250142</v>
+        <v>6.678776394916099</v>
       </c>
       <c r="C13">
         <v>471.28397822006644</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-10.899410680676526</v>
+        <v>-10.935141114158704</v>
       </c>
       <c r="B14">
-        <v>5.9854322433812879</v>
+        <v>5.8052288368566334</v>
       </c>
       <c r="C14">
         <v>471.28397822006644</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-8.6100547059888672</v>
+        <v>-8.66662786937979</v>
       </c>
       <c r="B15">
-        <v>5.1583364388898758</v>
+        <v>4.9225790948772374</v>
       </c>
       <c r="C15">
         <v>471.28397822006644</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-6.320781687914014</v>
+        <v>-6.3992805510435726</v>
       </c>
       <c r="B16">
-        <v>4.3310267133088178</v>
+        <v>4.0371269200175268</v>
       </c>
       <c r="C16">
         <v>471.28397822006644</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-4.0342583077003562</v>
+        <v>-4.1349876683238991</v>
       </c>
       <c r="B17">
-        <v>3.4966264676648584</v>
+        <v>3.1443330720562881</v>
       </c>
       <c r="C17">
         <v>471.28397822006644</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.7539280010795435</v>
+        <v>-1.8761879204423435</v>
       </c>
       <c r="B18">
-        <v>2.6462560780319184</v>
+        <v>2.2383358682720003</v>
       </c>
       <c r="C18">
         <v>471.28397822006644</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>0.52002553521180039</v>
+        <v>0.37698869588166206</v>
       </c>
       <c r="B19">
-        <v>1.77944184370385</v>
+        <v>1.3188228472026573</v>
       </c>
       <c r="C19">
         <v>471.28397822006644</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.7882335391858253</v>
+        <v>2.6249893595542324</v>
       </c>
       <c r="B20">
-        <v>0.89781154477947878</v>
+        <v>0.38686885270112431</v>
       </c>
       <c r="C20">
         <v>471.28397822006644</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5.0513272488546352</v>
+        <v>4.8682612494814359</v>
       </c>
       <c r="B21">
-        <v>0.0029929613576471902</v>
+        <v>-0.55645127137971551</v>
       </c>
       <c r="C21">
         <v>471.28397822006644</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>7.3098255401353853</v>
+        <v>7.1071719323606732</v>
       </c>
       <c r="B22">
-        <v>-0.90367587577857511</v>
+        <v>-1.5102540379169</v>
       </c>
       <c r="C22">
         <v>471.28397822006644</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>9.5637978405652344</v>
+        <v>9.3417705260544572</v>
       </c>
       <c r="B23">
-        <v>-1.8220159331091415</v>
+        <v>-2.4744213867070726</v>
       </c>
       <c r="C23">
         <v>471.28397822006644</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>11.813201215586338</v>
+        <v>11.57202653621658</v>
       </c>
       <c r="B24">
-        <v>-2.7521379264297576</v>
+        <v>-3.4490266142767743</v>
       </c>
       <c r="C24">
         <v>471.28397822006644</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>14.057992730640862</v>
+        <v>13.797909468500837</v>
       </c>
       <c r="B25">
-        <v>-3.6941525715361352</v>
+        <v>-4.4341430171525555</v>
       </c>
       <c r="C25">
         <v>471.28397822006644</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>16.298110928833516</v>
+        <v>16.01937568189016</v>
       </c>
       <c r="B26">
-        <v>-4.6482183479703307</v>
+        <v>-5.4298754913352916</v>
       </c>
       <c r="C26">
         <v>471.28397822006644</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>18.533420263919194</v>
+        <v>18.236328948684044</v>
       </c>
       <c r="B27">
-        <v>-5.6146847902597914</v>
+        <v>-6.4364553307232031</v>
       </c>
       <c r="C27">
         <v>471.28397822006644</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>20.763766667315302</v>
+        <v>20.448659894511067</v>
       </c>
       <c r="B28">
-        <v>-6.593949196678297</v>
+        <v>-7.4541454286888218</v>
       </c>
       <c r="C28">
         <v>471.28397822006644</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>22.988996070439295</v>
+        <v>22.656259144999854</v>
       </c>
       <c r="B29">
-        <v>-7.5864088654996458</v>
+        <v>-8.4832086786047043</v>
       </c>
       <c r="C29">
         <v>471.28397822006644</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>25.20903809914839</v>
+        <v>24.859076576600728</v>
       </c>
       <c r="B30">
-        <v>-8.5922452712656572</v>
+        <v>-9.5237655579542455</v>
       </c>
       <c r="C30">
         <v>471.28397822006644</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>27.424157157059177</v>
+        <v>27.057299069050963</v>
       </c>
       <c r="B31">
-        <v>-9.6107765935903142</v>
+        <v>-10.575366880664296</v>
       </c>
       <c r="C31">
         <v>471.28397822006644</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>29.634701342228045</v>
+        <v>29.251172752909572</v>
       </c>
       <c r="B32">
-        <v>-10.64110518835564</v>
+        <v>-11.637421044772571</v>
       </c>
       <c r="C32">
         <v>471.28397822006644</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>31.841018752711378</v>
+        <v>31.440943758735532</v>
       </c>
       <c r="B33">
-        <v>-11.682333411443654</v>
+        <v>-12.709336448316773</v>
       </c>
       <c r="C33">
         <v>471.28397822006644</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>34.0433222257771</v>
+        <v>33.626762386137472</v>
       </c>
       <c r="B34">
-        <v>-12.733912417153682</v>
+        <v>-13.790751829599978</v>
       </c>
       <c r="C34">
         <v>471.28397822006644</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>36.241283555539432</v>
+        <v>35.80839561092268</v>
       </c>
       <c r="B35">
-        <v>-13.796688553454329</v>
+        <v>-14.882227287986771</v>
       </c>
       <c r="C35">
         <v>471.28397822006644</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>38.434439275324074</v>
+        <v>37.985514577948</v>
       </c>
       <c r="B36">
-        <v>-14.871856966731482</v>
+        <v>-15.984553263107094</v>
       </c>
       <c r="C36">
         <v>471.28397822006644</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>40.622325918456767</v>
+        <v>40.15779043207035</v>
       </c>
       <c r="B37">
-        <v>-15.960612803371053</v>
+        <v>-17.098520194590897</v>
       </c>
       <c r="C37">
         <v>471.28397822006644</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>42.804148315966557</v>
+        <v>42.324659355384689</v>
       </c>
       <c r="B38">
-        <v>-17.065006573959089</v>
+        <v>-18.225483280997707</v>
       </c>
       <c r="C38">
         <v>471.28397822006644</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>44.97778448969553</v>
+        <v>44.484617678938157</v>
       </c>
       <c r="B39">
-        <v>-18.190510245882159</v>
+        <v>-19.369056756605307</v>
       </c>
       <c r="C39">
         <v>471.28397822006644</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>47.1407807591891</v>
+        <v>46.63592677101596</v>
       </c>
       <c r="B40">
-        <v>-19.34345115072697</v>
+        <v>-20.533419614621039</v>
       </c>
       <c r="C40">
         <v>471.28397822006644</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>49.29068344399267</v>
+        <v>48.776847999903325</v>
       </c>
       <c r="B41">
-        <v>-20.530156620080241</v>
+        <v>-21.722750848252264</v>
       </c>
       <c r="C41">
         <v>471.28397822006644</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>49.29068344399267</v>
+        <v>48.776847999903325</v>
       </c>
       <c r="B42">
-        <v>-20.530156620080241</v>
+        <v>-21.722750848252264</v>
       </c>
       <c r="C42">
         <v>471.28397822006644</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>47.024933258048435</v>
+        <v>46.553874756618</v>
       </c>
       <c r="B43">
-        <v>-19.642188319960546</v>
+        <v>-20.73064068674514</v>
       </c>
       <c r="C43">
         <v>471.28397822006644</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>44.765985379523492</v>
+        <v>44.3346054346843</v>
       </c>
       <c r="B44">
-        <v>-18.736678838177983</v>
+        <v>-19.729627741492944</v>
       </c>
       <c r="C44">
         <v>471.28397822006644</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>42.511390355309715</v>
+        <v>42.117305893580053</v>
       </c>
       <c r="B45">
-        <v>-17.819944605216463</v>
+        <v>-18.723880210625932</v>
       </c>
       <c r="C45">
         <v>471.28397822006644</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>40.258698732298988</v>
+        <v>39.900241992783073</v>
       </c>
       <c r="B46">
-        <v>-16.898302051559902</v>
+        <v>-17.717566292274366</v>
       </c>
       <c r="C46">
         <v>471.28397822006644</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>38.005792613079961</v>
+        <v>37.681914398783263</v>
       </c>
       <c r="B47">
-        <v>-15.977212621531022</v>
+        <v>-16.71428980000103</v>
       </c>
       <c r="C47">
         <v>471.28397822006644</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>35.751880323028111</v>
+        <v>35.461763006118623</v>
       </c>
       <c r="B48">
-        <v>-15.058717814807759</v>
+        <v>-15.715397009098735</v>
       </c>
       <c r="C48">
         <v>471.28397822006644</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>33.496501743215717</v>
+        <v>33.239462516339259</v>
       </c>
       <c r="B49">
-        <v>-14.144004144906852</v>
+        <v>-14.721669810292804</v>
       </c>
       <c r="C49">
         <v>471.28397822006644</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>31.239196754715049</v>
+        <v>31.014687630995258</v>
       </c>
       <c r="B50">
-        <v>-13.234258125345058</v>
+        <v>-13.733890094308574</v>
       </c>
       <c r="C50">
         <v>471.28397822006644</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>28.97964033578473</v>
+        <v>28.787208708773928</v>
       </c>
       <c r="B51">
-        <v>-12.330317893104107</v>
+        <v>-12.752609829385008</v>
       </c>
       <c r="C51">
         <v>471.28397822006644</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>26.718047853429034</v>
+        <v>26.5571787369115</v>
       </c>
       <c r="B52">
-        <v>-11.431628079025721</v>
+        <v>-11.777461293815678</v>
       </c>
       <c r="C52">
         <v>471.28397822006644</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>24.454769771838631</v>
+        <v>24.324846359781457</v>
       </c>
       <c r="B53">
-        <v>-10.537284937416619</v>
+        <v>-10.807846843407795</v>
       </c>
       <c r="C53">
         <v>471.28397822006644</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>22.190156555204165</v>
+        <v>22.090460221757244</v>
       </c>
       <c r="B54">
-        <v>-9.6463847225835071</v>
+        <v>-9.8431688339685586</v>
       </c>
       <c r="C54">
         <v>471.28397822006644</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>19.924474815437854</v>
+        <v>19.854209548700638</v>
       </c>
       <c r="B55">
-        <v>-8.758239919585094</v>
+        <v>-8.8829724402556121</v>
       </c>
       <c r="C55">
         <v>471.28397822006644</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>17.657655755338286</v>
+        <v>17.616045892426712</v>
       </c>
       <c r="B56">
-        <v>-7.8730279364880795</v>
+        <v>-7.9273741128283675</v>
       </c>
       <c r="C56">
         <v>471.28397822006644</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>15.389546725425587</v>
+        <v>15.375861386238828</v>
       </c>
       <c r="B57">
-        <v>-6.9911424121111443</v>
+        <v>-6.9766331211966488</v>
       </c>
       <c r="C57">
         <v>471.28397822006644</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>13.119995076219917</v>
+        <v>13.133548163440388</v>
       </c>
       <c r="B58">
-        <v>-6.1129769852729892</v>
+        <v>-6.0310087348703014</v>
       </c>
       <c r="C58">
         <v>471.28397822006644</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>10.848866523904174</v>
+        <v>10.889011337552217</v>
       </c>
       <c r="B59">
-        <v>-5.238877935064612</v>
+        <v>-5.0907290239739433</v>
       </c>
       <c r="C59">
         <v>471.28397822006644</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>8.5761002473123575</v>
+        <v>8.6422079429650278</v>
       </c>
       <c r="B60">
-        <v>-4.3690021016662808</v>
+        <v>-4.1558972610913321</v>
       </c>
       <c r="C60">
         <v>471.28397822006644</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>6.3016537909412271</v>
+        <v>6.3931079942869831</v>
       </c>
       <c r="B61">
-        <v>-3.5034589655305739</v>
+        <v>-3.2265855194210111</v>
       </c>
       <c r="C61">
         <v>471.28397822006644</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>4.0254846992875581</v>
+        <v>4.1416815061262673</v>
       </c>
       <c r="B62">
-        <v>-2.6423580071100776</v>
+        <v>-2.302865872161528</v>
       </c>
       <c r="C62">
         <v>471.28397822006644</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>1.7476627161583727</v>
+        <v>1.8879779323549688</v>
       </c>
       <c r="B63">
-        <v>-1.7855193773163172</v>
+        <v>-1.3846194514734371</v>
       </c>
       <c r="C63">
         <v>471.28397822006644</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-0.53129361739827574</v>
+        <v>-0.36763551609917938</v>
       </c>
       <c r="B64">
-        <v>-0.93160590889659178</v>
+        <v>-0.47096362536531988</v>
       </c>
       <c r="C64">
         <v>471.28397822006644</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.8107535610240317</v>
+        <v>-2.6247121890444811</v>
       </c>
       <c r="B65">
-        <v>-0.078991105057161365</v>
+        <v>0.43917517919221238</v>
       </c>
       <c r="C65">
         <v>471.28397822006644</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-5.0900863743605838</v>
+        <v>-4.8828054362892859</v>
       </c>
       <c r="B66">
-        <v>0.77395153099572978</v>
+        <v>1.3468705352285677</v>
       </c>
       <c r="C66">
         <v>471.28397822006644</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-7.36947638263249</v>
+        <v>-7.1420459222674877</v>
       </c>
       <c r="B67">
-        <v>1.626746677867484</v>
+        <v>2.2518083763563421</v>
       </c>
       <c r="C67">
         <v>471.28397822006644</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-9.6523681733958444</v>
+        <v>-9.40487356991522</v>
       </c>
       <c r="B68">
-        <v>2.470511741410113</v>
+        <v>3.148124078520913</v>
       </c>
       <c r="C68">
         <v>471.28397822006644</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-11.941429768488483</v>
+        <v>-11.673178312667492</v>
       </c>
       <c r="B69">
-        <v>3.298366665658365</v>
+        <v>4.0312749781322781</v>
       </c>
       <c r="C69">
         <v>471.28397822006644</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-14.232962664543484</v>
+        <v>-13.944340867452405</v>
       </c>
       <c r="B70">
-        <v>4.1198488201312555</v>
+        <v>4.9075568111260637</v>
       </c>
       <c r="C70">
         <v>471.28397822006644</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-16.522934456448652</v>
+        <v>-16.215505481863872</v>
       </c>
       <c r="B71">
-        <v>4.9453566102890569</v>
+        <v>5.7838336935801173</v>
       </c>
       <c r="C71">
         <v>471.28397822006644</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-18.812343657315424</v>
+        <v>-18.487379742665947</v>
       </c>
       <c r="B72">
-        <v>5.7723151598727762</v>
+        <v>6.6584048626155479</v>
       </c>
       <c r="C72">
         <v>471.28397822006644</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-21.102858196485709</v>
+        <v>-20.761145397005485</v>
       </c>
       <c r="B73">
-        <v>6.5964233619514836</v>
+        <v>7.5284298585435288</v>
       </c>
       <c r="C73">
         <v>471.28397822006644</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-23.393792749999772</v>
+        <v>-23.036317494390474</v>
       </c>
       <c r="B74">
-        <v>7.4194484686257587</v>
+        <v>8.3950743133922838</v>
       </c>
       <c r="C74">
         <v>471.28397822006644</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-25.683860823475</v>
+        <v>-25.311985317629606</v>
       </c>
       <c r="B75">
-        <v>8.2447079764865183</v>
+        <v>9.2605272364407334</v>
       </c>
       <c r="C75">
         <v>471.28397822006644</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-27.971724494138854</v>
+        <v>-27.587201780373302</v>
       </c>
       <c r="B76">
-        <v>9.0756520010544843</v>
+        <v>10.127065054253535</v>
       </c>
       <c r="C76">
         <v>471.28397822006644</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-30.256145049422674</v>
+        <v>-29.861090093241426</v>
       </c>
       <c r="B77">
-        <v>9.9154748234544989</v>
+        <v>10.996795226871091</v>
       </c>
       <c r="C77">
         <v>471.28397822006644</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-32.53633204596327</v>
+        <v>-32.1330910238899</v>
       </c>
       <c r="B78">
-        <v>10.766214768298074</v>
+        <v>11.871061930951017</v>
       </c>
       <c r="C78">
         <v>471.28397822006644</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-34.810938078431853</v>
+        <v>-34.40225088366725</v>
       </c>
       <c r="B79">
-        <v>11.631346403873447</v>
+        <v>12.752157462419188</v>
       </c>
       <c r="C79">
         <v>471.28397822006644</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-37.077599322462717</v>
+        <v>-36.666896131267372</v>
       </c>
       <c r="B80">
-        <v>12.516965348926153</v>
+        <v>13.64410436250216</v>
       </c>
       <c r="C80">
         <v>471.28397822006644</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-39.330510811927951</v>
+        <v>-38.922915987540755</v>
       </c>
       <c r="B81">
-        <v>13.438040930644721</v>
+        <v>14.556783342564271</v>
       </c>
       <c r="C81">
         <v>471.28397822006644</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-41.465147778311618</v>
+        <v>-41.096278841482686</v>
       </c>
       <c r="B82">
-        <v>14.664112268594032</v>
+        <v>15.66813755001701</v>
       </c>
       <c r="C82">
         <v>471.28397822006644</v>
